--- a/data/trans_dic/P33B_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R2-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,22</t>
+          <t>1,7; 8,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 11,7</t>
+          <t>4,73; 13,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,51</t>
+          <t>3,82; 9,38</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 9,86</t>
+          <t>3,73; 8,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 10,62</t>
+          <t>6,27; 11,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,4</t>
+          <t>5,55; 9,23</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 14,42</t>
+          <t>7,82; 13,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,21; 17,41</t>
+          <t>12,71; 17,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 15,02</t>
+          <t>10,97; 14,73</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 15,54</t>
+          <t>12,14; 17,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,45; 24,12</t>
+          <t>19,67; 24,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,32; 18,9</t>
+          <t>16,87; 20,51</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,3; 21,11</t>
+          <t>14,8; 20,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,78; 34,79</t>
+          <t>29,29; 35,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,71; 26,98</t>
+          <t>22,94; 26,89</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,46; 24,04</t>
+          <t>17,44; 23,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,38; 32,88</t>
+          <t>28,81; 35,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,02; 27,25</t>
+          <t>24,21; 28,88</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24,56; 32,92</t>
+          <t>25,35; 33,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>33,22; 40,14</t>
+          <t>33,85; 40,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,01; 36,31</t>
+          <t>31,3; 36,63</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,24; 14,6</t>
+          <t>12,84; 15,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,31; 22,4</t>
+          <t>21,33; 23,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,96; 18,27</t>
+          <t>17,55; 19,17</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>16218</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>30623</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36689</t>
+          <t>46842</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5885; 32861</t>
+          <t>6934; 34654</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11377; 36645</t>
+          <t>17135; 48326</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22335; 60671</t>
+          <t>29459; 72273</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>26551</t>
+          <t>28530</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>39195</t>
+          <t>42087</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65746</t>
+          <t>70616</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16336; 41743</t>
+          <t>17791; 42616</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23394; 54321</t>
+          <t>31430; 57702</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48796; 87928</t>
+          <t>54259; 90223</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59921</t>
+          <t>64131</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79895</t>
+          <t>94781</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>139816</t>
+          <t>158911</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45755; 77325</t>
+          <t>48579; 82866</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>66254; 94469</t>
+          <t>79070; 110979</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119584; 162052</t>
+          <t>136300; 183050</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>93733</t>
+          <t>103121</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>151207</t>
+          <t>164381</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>244941</t>
+          <t>267502</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41613; 137951</t>
+          <t>85076; 124001</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>124352; 171821</t>
+          <t>144846; 182089</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149103; 302415</t>
+          <t>242418; 294721</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>100735</t>
+          <t>105865</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>173266</t>
+          <t>196273</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>274001</t>
+          <t>302138</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>85689; 118278</t>
+          <t>89999; 124060</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>156863; 189614</t>
+          <t>177944; 214211</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>250972; 298200</t>
+          <t>278893; 326924</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>76105</t>
+          <t>83792</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>126962</t>
+          <t>140388</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>203066</t>
+          <t>224180</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>64285; 88504</t>
+          <t>71012; 97309</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>57095; 200057</t>
+          <t>126505; 154398</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>107656; 266112</t>
+          <t>204855; 244377</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>81780</t>
+          <t>91064</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>155682</t>
+          <t>171740</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>237462</t>
+          <t>262805</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>69445; 93077</t>
+          <t>78627; 104291</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>141442; 170911</t>
+          <t>157255; 189349</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>219709; 257281</t>
+          <t>242512; 283846</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>453796</t>
+          <t>492721</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>747925</t>
+          <t>840273</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1201720</t>
+          <t>1332994</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>354325; 505079</t>
+          <t>453359; 534440</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>596729; 819588</t>
+          <t>796552; 882039</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1064786; 1300366</t>
+          <t>1274926; 1392435</t>
         </is>
       </c>
     </row>
